--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D610B49-5D9B-451F-9242-370915564B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1C9134-9FCC-41A8-B22A-206BBADFE5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>sdadas</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>dsad</t>
+  </si>
+  <si>
+    <t>dasd</t>
   </si>
 </sst>
 </file>
@@ -368,6 +371,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L12" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J13" t="s">
         <v>1</v>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1C9134-9FCC-41A8-B22A-206BBADFE5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29458CC4-7DB0-4646-95D9-7ADCE1341171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>sdadas</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>dasd</t>
+  </si>
+  <si>
+    <t>das</t>
   </si>
 </sst>
 </file>
@@ -371,6 +374,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K11" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L12" t="s">
         <v>6</v>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29458CC4-7DB0-4646-95D9-7ADCE1341171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA76B4B-BE5B-456D-B0DE-5A5900A837C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>sdadas</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>das</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -369,27 +372,32 @@
   <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="J13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>5</v>
       </c>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA76B4B-BE5B-456D-B0DE-5A5900A837C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E8FA9C-0516-4FFA-9341-6B0506C083A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>sdadas</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>ss</t>
   </si>
 </sst>
 </file>
@@ -369,35 +372,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="K11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>5</v>
       </c>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E8FA9C-0516-4FFA-9341-6B0506C083A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EE197E-0BA6-41EA-ADF5-EA309668881D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <t>s</t>
   </si>
   <si>
-    <t>ss</t>
+    <t>css</t>
   </si>
 </sst>
 </file>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EE197E-0BA6-41EA-ADF5-EA309668881D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E62C89-878B-47FA-BAA1-6DF610826B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <t>s</t>
   </si>
   <si>
-    <t>css</t>
+    <t>qweqwe</t>
   </si>
 </sst>
 </file>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E62C89-878B-47FA-BAA1-6DF610826B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FC3FE6-E886-4FA2-98FE-5D7ED7FF547C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>sdadas</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>s</t>
-  </si>
-  <si>
-    <t>qweqwe</t>
   </si>
 </sst>
 </file>
@@ -385,7 +382,7 @@
         <v>8</v>
       </c>
       <c r="P9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FC3FE6-E886-4FA2-98FE-5D7ED7FF547C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06A835D-8B7F-4E1C-8A1B-93938E789F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>sdadas</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>dads</t>
   </si>
 </sst>
 </file>
@@ -405,17 +408,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="13:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="13:16" x14ac:dyDescent="0.3">
       <c r="N21" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="P21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="13:16" x14ac:dyDescent="0.3">
       <c r="M22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="13:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="13:16" x14ac:dyDescent="0.3">
       <c r="O24" t="s">
         <v>2</v>
       </c>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06A835D-8B7F-4E1C-8A1B-93938E789F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235163CC-C280-480B-B242-74765E5B0418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <t>s</t>
   </si>
   <si>
-    <t>dads</t>
+    <t>saxasx</t>
   </si>
 </sst>
 </file>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235163CC-C280-480B-B242-74765E5B0418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067C9557-11EE-48BA-99BC-D9E540E53F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <t>s</t>
   </si>
   <si>
-    <t>saxasx</t>
+    <t>dasda</t>
   </si>
 </sst>
 </file>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067C9557-11EE-48BA-99BC-D9E540E53F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD44A218-AC60-4C0C-96EA-162EE964CC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>sdadas</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>dasda</t>
+  </si>
+  <si>
+    <t>dsd</t>
   </si>
 </sst>
 </file>
@@ -380,6 +383,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M9" t="s">
         <v>8</v>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD44A218-AC60-4C0C-96EA-162EE964CC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38B3438-F431-455D-AE1B-DBAD5FA167FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>sdadas</t>
   </si>
@@ -416,6 +416,11 @@
         <v>5</v>
       </c>
     </row>
+    <row r="18" spans="13:16" x14ac:dyDescent="0.3">
+      <c r="O18" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="21" spans="13:16" x14ac:dyDescent="0.3">
       <c r="N21" t="s">
         <v>4</v>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38B3438-F431-455D-AE1B-DBAD5FA167FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED27A2D-DBB2-455A-9BA3-F6FCCC379A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>sdadas</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>dsd</t>
+  </si>
+  <si>
+    <t>sAS</t>
   </si>
 </sst>
 </file>
@@ -416,12 +419,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="13:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="12:16" x14ac:dyDescent="0.3">
       <c r="O18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="13:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="12:16" x14ac:dyDescent="0.3">
+      <c r="L19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="12:16" x14ac:dyDescent="0.3">
       <c r="N21" t="s">
         <v>4</v>
       </c>
@@ -429,12 +437,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="13:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="12:16" x14ac:dyDescent="0.3">
       <c r="M22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="13:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="12:16" x14ac:dyDescent="0.3">
       <c r="O24" t="s">
         <v>2</v>
       </c>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED27A2D-DBB2-455A-9BA3-F6FCCC379A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BFC45C-4C3F-46AA-9AC3-CAA62C87131B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>sdadas</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>sAS</t>
+  </si>
+  <si>
+    <t>dsa</t>
   </si>
 </sst>
 </file>
@@ -429,6 +432,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="20" spans="12:16" x14ac:dyDescent="0.3">
+      <c r="O20" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="21" spans="12:16" x14ac:dyDescent="0.3">
       <c r="N21" t="s">
         <v>4</v>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BFC45C-4C3F-46AA-9AC3-CAA62C87131B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BDDDDD-406E-4068-B742-62EC74D1B789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
     <t>sAS</t>
   </si>
   <si>
-    <t>dsa</t>
+    <t>sdasdasdas</t>
   </si>
 </sst>
 </file>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BDDDDD-406E-4068-B742-62EC74D1B789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E16D9F-CD86-4097-9999-F887380499E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>sdadas</t>
   </si>
@@ -422,6 +422,11 @@
         <v>5</v>
       </c>
     </row>
+    <row r="17" spans="12:16" x14ac:dyDescent="0.3">
+      <c r="P17" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="18" spans="12:16" x14ac:dyDescent="0.3">
       <c r="O18" t="s">
         <v>6</v>

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E16D9F-CD86-4097-9999-F887380499E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B9E241-3D56-4754-93FB-7584DBAEBB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>sdadas</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>sdasdasdas</t>
+  </si>
+  <si>
+    <t>вфывыф</t>
+  </si>
+  <si>
+    <t>dasdsad</t>
   </si>
 </sst>
 </file>
@@ -417,6 +423,16 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>5</v>
@@ -435,6 +451,9 @@
     <row r="19" spans="12:16" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
         <v>11</v>
+      </c>
+      <c r="N19" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="12:16" x14ac:dyDescent="0.3">

--- a/test4.xlsx
+++ b/test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_year\nirs\total\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B9E241-3D56-4754-93FB-7584DBAEBB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0F2C2C-153C-4750-92BC-D9538F1F0A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,13 +63,13 @@
     <t>sAS</t>
   </si>
   <si>
-    <t>sdasdasdas</t>
-  </si>
-  <si>
     <t>вфывыф</t>
   </si>
   <si>
     <t>dasdsad</t>
+  </si>
+  <si>
+    <t>xasdasdasds</t>
   </si>
 </sst>
 </file>
@@ -425,7 +425,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -453,12 +453,12 @@
         <v>11</v>
       </c>
       <c r="N19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="12:16" x14ac:dyDescent="0.3">
       <c r="O20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="12:16" x14ac:dyDescent="0.3">
